--- a/inst/templates/imurun_template.xlsx
+++ b/inst/templates/imurun_template.xlsx
@@ -386,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="100.711"/>
@@ -542,229 +542,243 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">  Advanced settings may be added as extra rows, e.g. cores, thin, adapt_delta,</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>observations sheet -- one row per sampled count:</t>
+          <t xml:space="preserve">  max_treedepth, df, or dose_schedule (the age each dose is given, e.g. 1, 4).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          the location of this count (must match a Location in the locations sheet)</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Observation Year  timing of the observation</t>
+          <t>observations sheet -- one row per sampled count:</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Youngest age      youngest age this count covers</t>
+          <t xml:space="preserve">  Location          the location of this count (must match a Location in the locations sheet)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Oldest age        oldest age this count covers (put the same age in both for a single age)</t>
+          <t xml:space="preserve">  Observation Year  timing of the observation</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dose              which dose this count is for: 1 or 2</t>
+          <t xml:space="preserve">  Youngest age      youngest age this count covers</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Vaccinated        how many were found vaccinated</t>
+          <t xml:space="preserve">  Oldest age        oldest age this count covers (for a single age, repeat it or leave blank)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sampled           how many were sampled (Vaccinated must be &lt;= Sampled)</t>
+          <t xml:space="preserve">  Dose              which dose this count is for (1 = first dose, 2 = second, ...)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Censored          optional; leave blank, or put 1 for a right-censored observation</t>
+          <t xml:space="preserve">  Vaccinated        how many were found vaccinated</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A count covering several ages is split evenly across them, and the cohort of each age</t>
+          <t xml:space="preserve">  Sampled           how many were sampled (Vaccinated must be &lt;= Sampled)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  is derived as Observation Year - age (a snapshot in time). If you prefer,</t>
+          <t xml:space="preserve">  Censored          optional; leave blank, or put 1 for a right-censored observation</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  you may use a single 'Age' column instead of the two age columns.</t>
+          <t xml:space="preserve">  A count covering several ages is split evenly across them, and the cohort of each age</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">  is derived as Observation Year - age (a snapshot in time). If you prefer,</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>locations sheet -- your location hierarchy, written as a tree:</t>
+          <t xml:space="preserve">  you may use a single 'Age' column instead of the two age columns.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          a unique name for the location (you choose the names)</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Parent location   the name of this location's parent (must be another Location in this sheet)</t>
+          <t>locations sheet -- your location hierarchy, written as a tree:</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  IMPORTANT: there must be exactly ONE root -- the single top location whose Parent location</t>
+          <t xml:space="preserve">  Location          a unique name for the location (you choose the names)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  is left BLANK. Every other location must name its parent, and the parents must chain up to</t>
+          <t xml:space="preserve">  Parent location   the name of this location's parent (must be another Location in this sheet)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  that one root (no loops, no second root). This is the most common thing to get wrong.</t>
+          <t xml:space="preserve">  IMPORTANT: there must be exactly ONE root -- the single top location whose Parent location</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">  is left BLANK. Every other location must name its parent, and the parents must chain up to</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>target sheet -- the populations to predict coverage for (required):</t>
+          <t xml:space="preserve">  that one root (no loops, no second root). This is the most common thing to get wrong.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          one or more locations to predict, ';'-separated</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
+          <t>target sheet -- the populations to predict coverage for (required):</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Youngest age      youngest age to predict</t>
+          <t xml:space="preserve">  Location          one or more locations to predict, ';'-separated</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Oldest age        oldest age to predict</t>
+          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dose              optional; leave blank to default to the final dose</t>
+          <t xml:space="preserve">  Youngest age      youngest age to predict</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Label             optional; free-text label echoed into the results</t>
+          <t xml:space="preserve">  Oldest age        oldest age to predict</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A Location-only row (year/ages/dose left blank) inherits those from the row above it.</t>
+          <t xml:space="preserve">  Dose              optional; leave blank to default to the final dose</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">  Label             optional; free-text label echoed into the results</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Check from R: imuRUN::run_fit('yourfile.xlsx', dryrun = TRUE)</t>
+          <t xml:space="preserve">  A Location-only row (year/ages/dose left blank) inherits those from the row above it.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Fit from R:   imuRUN::run_fit('yourfile.xlsx')</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Check from R: imuRUN::run_fit('yourfile.xlsx', dryrun = TRUE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Fit from R:   imuRUN::run_fit('yourfile.xlsx')</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>If you installed the optional command wrapper, 'imurun yourfile.xlsx' also works.</t>
         </is>
@@ -940,8 +954,8 @@
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1001">
-      <formula1>"1,2"</formula1>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1001">
+      <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1" gridLinesSet="1"/>
@@ -1027,8 +1041,8 @@
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1001">
-      <formula1>"1,2"</formula1>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1001">
+      <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1" gridLinesSet="1"/>

--- a/inst/templates/imurun_template.xlsx
+++ b/inst/templates/imurun_template.xlsx
@@ -386,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="100.711"/>
@@ -521,250 +521,243 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  seed              optional random seed for reproducibility</t>
+          <t xml:space="preserve">  Add optional settings as extra rows when needed, e.g. seed, warmup, cores,</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  warmup            optional warmup iterations per chain</t>
+          <t xml:space="preserve">  thin, adapt_delta, max_treedepth, df, or dose_schedule (dose ages, e.g. 1, 4).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Leave seed/warmup blank to use the model defaults.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>observations sheet -- one row per sampled count:</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>observations sheet -- one row per sampled count:</t>
+          <t xml:space="preserve">  Location          the location of this count (must match a Location in the locations sheet)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          the location of this count (must match a Location in the locations sheet)</t>
+          <t xml:space="preserve">  Observation Year  timing of the observation</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Observation Year  timing of the observation</t>
+          <t xml:space="preserve">  Youngest age      youngest age this count covers</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Youngest age      youngest age this count covers</t>
+          <t xml:space="preserve">  Oldest age        oldest age covered; for one age, repeat Youngest age or leave blank</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Oldest age        oldest age this count covers (put the same age in both for a single age)</t>
+          <t xml:space="preserve">  Dose              which dose this count is for (1 = first dose, 2 = second, ...)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dose              which dose this count is for: 1 or 2</t>
+          <t xml:space="preserve">  Vaccinated        how many were found vaccinated</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Vaccinated        how many were found vaccinated</t>
+          <t xml:space="preserve">  Sampled           how many were sampled (Vaccinated must be &lt;= Sampled)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sampled           how many were sampled (Vaccinated must be &lt;= Sampled)</t>
+          <t xml:space="preserve">  Censored          optional; leave blank, or put 1 for a right-censored observation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Censored          optional; leave blank, or put 1 for a right-censored observation</t>
+          <t xml:space="preserve">  A count covering several ages is split evenly across them, and the cohort of each age</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A count covering several ages is split evenly across them, and the cohort of each age</t>
+          <t xml:space="preserve">  is derived as Observation Year - age (a snapshot in time). If you prefer,</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  is derived as Observation Year - age (a snapshot in time). If you prefer,</t>
+          <t xml:space="preserve">  you may use a single 'Age' column instead of the two age columns.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  you may use a single 'Age' column instead of the two age columns.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>locations sheet -- your location hierarchy, written as a tree:</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>locations sheet -- your location hierarchy, written as a tree:</t>
+          <t xml:space="preserve">  Location          a unique name for the location (you choose the names)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          a unique name for the location (you choose the names)</t>
+          <t xml:space="preserve">  Parent location   the name of this location's parent (must be another Location in this sheet)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Parent location   the name of this location's parent (must be another Location in this sheet)</t>
+          <t xml:space="preserve">  IMPORTANT: there must be exactly ONE root -- the single top location whose Parent location</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  IMPORTANT: there must be exactly ONE root -- the single top location whose Parent location</t>
+          <t xml:space="preserve">  is left BLANK. Every other location must name its parent, and the parents must chain up to</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  is left BLANK. Every other location must name its parent, and the parents must chain up to</t>
+          <t xml:space="preserve">  that one root (no loops, no second root). This is the most common thing to get wrong.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  that one root (no loops, no second root). This is the most common thing to get wrong.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>target sheet -- the populations to predict coverage for (required):</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>target sheet -- the populations to predict coverage for (required):</t>
+          <t xml:space="preserve">  Location          one or more locations to predict, ';'-separated</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          one or more locations to predict, ';'-separated</t>
+          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
+          <t xml:space="preserve">  Youngest age      youngest age to predict</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Youngest age      youngest age to predict</t>
+          <t xml:space="preserve">  Oldest age        oldest age to predict</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Oldest age        oldest age to predict</t>
+          <t xml:space="preserve">  Dose              optional; leave blank to default to the final dose</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dose              optional; leave blank to default to the final dose</t>
+          <t xml:space="preserve">  Label             optional; free-text label echoed into the results</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Label             optional; free-text label echoed into the results</t>
+          <t xml:space="preserve">  A Location-only row (year/ages/dose left blank) inherits those from the row above it.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A Location-only row (year/ages/dose left blank) inherits those from the row above it.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>Check from R: imuRUN::run_fit('yourfile.xlsx', dryrun = TRUE)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Check from R: imuRUN::run_fit('yourfile.xlsx', dryrun = TRUE)</t>
+          <t>Fit from R:   imuRUN::run_fit('yourfile.xlsx')</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Fit from R:   imuRUN::run_fit('yourfile.xlsx')</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>If you installed the optional command wrapper, 'imurun yourfile.xlsx' also works.</t>
         </is>
@@ -779,12 +772,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,40 +828,6 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Number of chains</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Optional random seed for reproducibility</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>warmup</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Optional warmup iterations per chain</t>
         </is>
       </c>
     </row>
@@ -940,8 +899,8 @@
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1001">
-      <formula1>"1,2"</formula1>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1001">
+      <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1" gridLinesSet="1"/>
@@ -1027,8 +986,8 @@
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1001">
-      <formula1>"1,2"</formula1>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1001">
+      <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1" gridLinesSet="1"/>

--- a/inst/templates/imurun_template.xlsx
+++ b/inst/templates/imurun_template.xlsx
@@ -556,7 +556,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Observation Year  timing of the observation</t>
+          <t xml:space="preserve">  Observation Year  calendar year of the observation (1000-9999)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
+          <t xml:space="preserve">  Target Year       calendar year of the target snapshot (1000-9999)</t>
         </is>
       </c>
     </row>
